--- a/data/seed/portfolio/L-2025-2395/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-2395/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,183 +540,183 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>13282000</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>1832000</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6435</t>
+          <t>Оплата по счет-фактуре №977 за поставленный товар</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>125118000</v>
+        <v>140232000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>5452000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>1736000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>370112444</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000154627596001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №18/26</t>
+          <t>Оплата за продукцию по договору №218/26, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>119666000</v>
+        <v>141968000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>23786000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>6139000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6435</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>143452000</v>
+        <v>135829000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>17531000</v>
+        <v>3188000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5170 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №108/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>160983000</v>
+        <v>139017000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>4804000</v>
+        <v>1966000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>312713817</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000132397891001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,11 +726,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2535 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №269/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>165787000</v>
+        <v>140983000</v>
       </c>
     </row>
     <row r="13">
@@ -740,23 +740,23 @@
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>3615000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>25254000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -766,11 +766,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №75/26</t>
+          <t>Оплата за продукцию по договору №69/26, НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>162172000</v>
+        <v>166237000</v>
       </c>
     </row>
     <row r="14">
@@ -780,18 +780,23 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>14705000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>12861000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -801,197 +806,192 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА ИЮНЬ 2026 Г. СОГЛАСНО РЕЕСТРУ №609</t>
+          <t>Оплата за продукцию по договору №86/26, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>147467000</v>
+        <v>179098000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>80010000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>12611000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №81/26</t>
+          <t>Оплата за продукцию по дог. №19/26, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>67457000</v>
+        <v>191709000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>6173000</v>
+        <v>2932000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №27/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №4675 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>73630000</v>
+        <v>194641000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>4006000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>14705000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>246439969</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №116/26, НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77636000</v>
+        <v>179936000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1668000</v>
+        <v>18054000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>351622961</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000622483227001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №44/21</t>
+          <t>Оплата за транспортные услуги по договору №75/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>75968000</v>
+        <v>161882000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>6634000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>11055000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>370112444</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000154627596001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,211 +1001,211 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №160/26 от 09.07.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4647 07.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>69334000</v>
+        <v>172937000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>1982000</v>
+        <v>9690000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №155/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №651 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>71316000</v>
+        <v>182627000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6740000</v>
+        <v>13583000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №158/26</t>
+          <t>Предоплата за материалы по дог. №81/26</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>64576000</v>
+        <v>169044000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>27329000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>1668000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Ziyo Qurilish MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>365029789</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000252332057001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6220 13.07.2026, QQS bilan</t>
+          <t>Арендная плата за июль 2026 г. по договору №82/22</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>91905000</v>
+        <v>167376000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>1977000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>4109000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Mehnat Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>295007701</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000939368176001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №184/26 от 13.07.2026</t>
+          <t>Оплата за сырье по дог. №160/26 от 09.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>93882000</v>
+        <v>163267000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>1878000</v>
+        <v>2288000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Shartnoma №117/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №89/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>95760000</v>
+        <v>165555000</v>
       </c>
     </row>
     <row r="25">
@@ -1215,37 +1215,37 @@
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>6485000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>20436000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Urganch Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>286331312</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000937734309001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №75/26</t>
+          <t>Оплата по счет-фактуре №3892 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>89275000</v>
+        <v>185991000</v>
       </c>
     </row>
     <row r="26">
@@ -1255,23 +1255,23 @@
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>10686000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>18527000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,136 +1281,136 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №258/26</t>
+          <t>Предоплата за товар по дог. №228/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78589000</v>
+        <v>204518000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>3986000</v>
+        <v>14339000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Navro'z Ip-Kalava MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>389741736</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000651397089001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1725 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №246/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>82575000</v>
+        <v>218857000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>5583000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>5707000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №105/26</t>
+          <t>Предоплата за товар по договору №11/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>76992000</v>
+        <v>224564000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2005000</v>
+        <v>40742000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>294061548</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000991807299001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №75/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>74987000</v>
+        <v>183822000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
@@ -1441,131 +1441,131 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>72982000</v>
+        <v>181817000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5270000</v>
+        <v>2005000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №252/26</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>67712000</v>
+        <v>179812000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>20042000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>13366000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9130 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №105/26</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>87754000</v>
+        <v>166446000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>3172000</v>
+        <v>7937000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №81/26, НДС 12%</t>
+          <t>Shartnoma №210/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>90926000</v>
+        <v>174383000</v>
       </c>
     </row>
     <row r="34">
@@ -1575,103 +1575,103 @@
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>8992000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>15440000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nurafshon Trans Servis AJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>224458725</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000307962555001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №646от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №3867</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>99918000</v>
+        <v>158943000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>5733000</v>
+        <v>25643000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9523 за поставленный товар</t>
+          <t>Оплата по с/ф №9653 за поставленный товар</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>105651000</v>
+        <v>184586000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>2542000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>11572000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1681,11 +1681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3867</t>
+          <t>Оплата по с/ф №9722 за поставленный товар</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>103109000</v>
+        <v>196158000</v>
       </c>
     </row>
     <row r="37">
@@ -1697,35 +1697,35 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>10482000</v>
+        <v>2104000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7319 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>113591000</v>
+        <v>198262000</v>
       </c>
     </row>
     <row r="38">
@@ -1735,37 +1735,37 @@
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>7324000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>4953000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4159 ОТ 20.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №7112</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>120915000</v>
+        <v>193309000</v>
       </c>
     </row>
     <row r="39">
@@ -1775,37 +1775,37 @@
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>4398000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>10985000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №258/26 от 20.07.2026</t>
+          <t>Предоплата за материалы по договору №268/26</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>125313000</v>
+        <v>182324000</v>
       </c>
     </row>
     <row r="40">
@@ -1815,183 +1815,183 @@
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>2154000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>13422000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №205/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №63/26 ОТ 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>127467000</v>
+        <v>168902000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>3047000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>9130000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №63/26 ОТ 20.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №42/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>124420000</v>
+        <v>178032000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3388000</v>
+        <v>2845000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7112</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>121032000</v>
+        <v>175187000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>6344000</v>
+        <v>5122000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №268/26</t>
+          <t>Оплата за транспортные услуги по договору №146/26</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>114688000</v>
+        <v>170065000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>7270000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>4065000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2001,152 +2001,152 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №146/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №255/26, QQS 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>107418000</v>
+        <v>174130000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>3545000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>26600000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Navro'z Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>389741736</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000651397089001</t>
+          <t>16307000206639712417</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №32 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>110963000</v>
+        <v>147530000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>2729000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>3367000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата за продукцию по договору №145/26, НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>108234000</v>
+        <v>150897000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>6599000</v>
+        <v>3165000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4817 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №9106 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>114833000</v>
+        <v>154062000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>2114000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16307000206639712417</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2156,11 +2156,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по счет-фактуре №5203 за поставленный товар</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>88233000</v>
+        <v>156176000</v>
       </c>
     </row>
     <row r="49">
@@ -2170,37 +2170,37 @@
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>24339000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1043000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000540864458001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2897 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>112572000</v>
+        <v>155133000</v>
       </c>
     </row>
     <row r="50">
@@ -2210,37 +2210,37 @@
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>8586000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5957 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №102/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>121158000</v>
+        <v>150783000</v>
       </c>
     </row>
     <row r="51">
@@ -2250,37 +2250,37 @@
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>2287000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>8813000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6288 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №258/26</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>123445000</v>
+        <v>141970000</v>
       </c>
     </row>
     <row r="52">
@@ -2291,377 +2291,377 @@
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1043000</v>
+        <v>12259000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Denov Savdo MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>325032138</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000702205650001</t>
+          <t>20208000022391100001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Предоплата за материалы по договору №36/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>122402000</v>
+        <v>129711000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>2458000</v>
+        <v>18380000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №102/26</t>
+          <t>Оплата за товары согласно счет-фактуре №5851</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>119944000</v>
+        <v>111331000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>4374000</v>
+        <v>7284000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ishonch Sut Mahsulotlari MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>390950077</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000119393681001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №36/26</t>
+          <t>Оплата за транспортные услуги по дог. №123/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>115570000</v>
+        <v>104047000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>5765000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>16206000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5851</t>
+          <t>Оплата за товар по счет-фактуре №6060 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>109805000</v>
+        <v>120253000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>3448000</v>
+        <v>7338000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №266 ОТ 29.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №9428 за поставленный товар</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>113253000</v>
+        <v>127591000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>9121000</v>
+        <v>300000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>255250321</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №291/26</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>104132000</v>
+        <v>127291000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>3424000</v>
+        <v>16281000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Afrosiyob Moy MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>323269310</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000303426573001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №42/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №89/26, НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>107556000</v>
+        <v>143572000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>2959000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>9057000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Denov Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>245872503</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000796255585001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №123/26</t>
+          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>104597000</v>
+        <v>152629000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>19472000</v>
+        <v>2354000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>346286181</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000345569865001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №13/26 от 31.07.2026</t>
+          <t>Shartnoma №111/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>124069000</v>
+        <v>154983000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>1971000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2671,11 +2671,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата по счет-фактуре №5956 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>123769000</v>
+        <v>156954000</v>
       </c>
     </row>
     <row r="62">
@@ -2687,35 +2687,35 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>19452000</v>
+        <v>1642000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №90/26 от 03.08.2026</t>
+          <t>Предоплата за товар по договору №194/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>143221000</v>
+        <v>158596000</v>
       </c>
     </row>
     <row r="63">
@@ -2725,103 +2725,103 @@
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>5906000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>957000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №255/26 от 03.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №218/26, QQS bilan</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>149127000</v>
+        <v>157639000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>3018000</v>
+        <v>6221000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2566 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2973 05.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>152145000</v>
+        <v>163860000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>2511000</v>
+        <v>4733000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>312713817</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000132397891001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2831,117 +2831,117 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №190/26 от 03.08.2026</t>
+          <t>Оплата за продукцию по дог. №135/26, НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>154656000</v>
+        <v>168593000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>1014000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>2089000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Afrosiyob Moy MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>323269310</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000303426573001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №196/26</t>
+          <t>Оплата по счет-фактуре №7127 за поставленный товар</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>153642000</v>
+        <v>170682000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>9599000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>18240000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4747</t>
+          <t>Предоплата за товар по договору №287/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>144043000</v>
+        <v>188922000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>101206000</v>
+        <v>728000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2951,112 +2951,112 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №250/26</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №1491</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>42837000</v>
+        <v>188194000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>2228000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>13864000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>246439969</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №281/26 от 04.08.2026</t>
+          <t>Iyul oyi uchun ish haqi, reestr №5944</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>45065000</v>
+        <v>174330000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>3817000</v>
+        <v>89637000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №71/26</t>
+          <t>Предоплата за материалы по договору №47/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>41248000</v>
+        <v>84693000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>13864000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>16169000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3066,91 +3066,91 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за товар по счет-фактуре №219 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>27384000</v>
+        <v>100862000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>5928000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>1253000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2164 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Tovarlar uchun to'lov h/f №5929</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>33312000</v>
+        <v>99609000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>1523000</v>
+        <v>1327000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Ishonch Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>294061548</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000991807299001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №165/26</t>
+          <t>Оплата за товары согласно счет-фактуре №6985</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>31789000</v>
+        <v>98282000</v>
       </c>
     </row>
     <row r="74">
@@ -3160,37 +3160,37 @@
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>4255000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>1573000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Ziyo Qurilish MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>365029789</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000252332057001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9366 за поставленный товар</t>
+          <t>Арендная плата за август 2026 г. по договору №82/22</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>36044000</v>
+        <v>96709000</v>
       </c>
     </row>
     <row r="75">
@@ -3200,37 +3200,37 @@
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>2561000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>2004000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №209/26 от 07.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №5282</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>38605000</v>
+        <v>94705000</v>
       </c>
     </row>
     <row r="76">
@@ -3240,37 +3240,37 @@
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>2281000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>6757000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9551 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №2690</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>40886000</v>
+        <v>87948000</v>
       </c>
     </row>
     <row r="77">
@@ -3281,36 +3281,36 @@
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>8498000</v>
+        <v>7626000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Denov Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>325032138</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000022391100001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2773</t>
+          <t>Tovarlar uchun to'lov h/f №7957</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>32388000</v>
+        <v>80322000</v>
       </c>
     </row>
     <row r="78">
@@ -3322,35 +3322,35 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>4171000</v>
+        <v>6207000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №82/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №38/26, QQS 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>36559000</v>
+        <v>86529000</v>
       </c>
     </row>
     <row r="79">
@@ -3360,23 +3360,23 @@
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>1573000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>1746000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>351622961</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000622483227001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3386,11 +3386,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по дог. №44/21</t>
+          <t>Оплата за товар по с/ф №3638 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>34986000</v>
+        <v>88275000</v>
       </c>
     </row>
     <row r="80">
@@ -3401,116 +3401,116 @@
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>11389000</v>
+        <v>1537000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Mehnat Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>295007701</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000939368176001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №214/26 ОТ 10.08.2026, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №8014</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>23597000</v>
+        <v>86738000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1510000</v>
+        <v>1538000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ishonch Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>390950077</t>
+          <t>294061548</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000119393681001</t>
+          <t>20208000991807299001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №103/26</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №648</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>22087000</v>
+        <v>85200000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>2390000</v>
+        <v>2541000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>370112444</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000154627596001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №298/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №219/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>19697000</v>
+        <v>82659000</v>
       </c>
     </row>
     <row r="83">
@@ -3520,63 +3520,63 @@
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>6111000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2956000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6953</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9806</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>13586000</v>
+        <v>85615000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>1903000</v>
+        <v>2096000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>312713817</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000132397891001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3586,171 +3586,171 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9768 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>15489000</v>
+        <v>87711000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>5048000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>17118000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №294/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №175/26, QQS bilan</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>20537000</v>
+        <v>70593000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>9270000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Оплата за товар о счет-фактуре №1776 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>18647000</v>
+        <v>79863000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>4509000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Оплата по счет-фактуре №5524 за поставленный товар</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>16757000</v>
+        <v>84372000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>2723000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>11485000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №95/26</t>
+          <t>Предоплата за товар по дог. №97/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>14034000</v>
+        <v>95857000</v>
       </c>
     </row>
     <row r="89">
@@ -3762,35 +3762,35 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>2663000</v>
+        <v>3990000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №166/26, НДС 12%</t>
+          <t>Shartnoma №273/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>16697000</v>
+        <v>99847000</v>
       </c>
     </row>
     <row r="90">
@@ -3800,37 +3800,37 @@
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>910000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>3252000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8222</t>
+          <t>Оплата за товар по счет-фактуре №8818 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>15787000</v>
+        <v>103099000</v>
       </c>
     </row>
     <row r="91">
@@ -3840,37 +3840,37 @@
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>1567000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>1852000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №133/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3834 за поставленный товар</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>14220000</v>
+        <v>104951000</v>
       </c>
     </row>
     <row r="92">
@@ -3881,22 +3881,22 @@
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>4555000</v>
+        <v>635000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3906,232 +3906,237 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9189</t>
+          <t>Предоплата за материалы по договору №273/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>9665000</v>
+        <v>104316000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>12248000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №243/26, НДС 12%</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>21913000</v>
+        <v>102426000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>2456000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4477 от 18.08.2026, в т.ч. НДС 12%</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>24369000</v>
+        <v>100536000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>2875000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>7690000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8589</t>
+          <t>Оплата за сырье по дог. №125/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>27244000</v>
+        <v>92846000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>2451000</v>
+        <v>3911000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3157 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>29695000</v>
+        <v>96757000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>2405000</v>
+        <v>2563000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №651 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №251/26, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>32100000</v>
+        <v>99320000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>1848000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>16307000206639712417</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4141,77 +4146,77 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>5500000</v>
+        <v>101168000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>16441000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>13055000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Denov Savdo MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>325032138</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000022391100001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №290/26 от 21.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №171/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>21941000</v>
+        <v>88113000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>11574000</v>
+        <v>1964000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>312713817</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000132397891001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4221,51 +4226,46 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1395 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №6314 за поставленный товар</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>33515000</v>
+        <v>90077000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>9886000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>26600000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>246439969</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>16307000206639712417</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2965 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>43401000</v>
+        <v>63477000</v>
       </c>
     </row>
     <row r="102">
@@ -4277,35 +4277,35 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>3392000</v>
+        <v>9238000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №85/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №954 за поставленный товар</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46793000</v>
+        <v>72715000</v>
       </c>
     </row>
     <row r="103">
@@ -4317,35 +4317,35 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>1862000</v>
+        <v>3180000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9176 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №134/26, НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>48655000</v>
+        <v>75895000</v>
       </c>
     </row>
     <row r="104">
@@ -4356,116 +4356,116 @@
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>2126000</v>
+        <v>2117000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Mehnat Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>295007701</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000939368176001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №109/26 от 21.08.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6752</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46529000</v>
+        <v>73778000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>8067000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>2262000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Ishonch Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>294061548</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000991807299001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №287/26 от 24.08.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №152/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>54596000</v>
+        <v>71516000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>3320000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2656000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nurafshon Trans Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>224458725</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000307962555001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №163/26 от 24.08.2026</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>57916000</v>
+        <v>68860000</v>
       </c>
     </row>
     <row r="107">
@@ -4477,35 +4477,35 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>2094000</v>
+        <v>5951000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5992 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №142/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>60010000</v>
+        <v>74811000</v>
       </c>
     </row>
     <row r="108">
@@ -4516,76 +4516,76 @@
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2506000</v>
+        <v>5923000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6308</t>
+          <t>Оплата за товары согласно счет-фактуре №7989</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>57504000</v>
+        <v>68888000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2527000</v>
+        <v>983000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000540864458001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>54977000</v>
+        <v>67905000</v>
       </c>
     </row>
     <row r="110">
@@ -4595,103 +4595,103 @@
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>3669000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>2437000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №291/26 от 25.08.2026</t>
+          <t>Оплата за товары согласно с/ф №2999</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>58646000</v>
+        <v>65468000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>3297000</v>
+        <v>10853000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1136 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4544 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>61943000</v>
+        <v>76321000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>5068000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>2102000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4701,117 +4701,117 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №729</t>
+          <t>Оплата за продукцию по договору №199/26, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>56875000</v>
+        <v>78423000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>29195000</v>
+        <v>3114000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6835 26.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №147/26, QQS 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>86070000</v>
+        <v>81537000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>3122000</v>
+        <v>2303000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7197</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №771</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>89192000</v>
+        <v>83840000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>983000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>1626000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Afrosiyob Moy MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>323269310</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000702205650001</t>
+          <t>20208000303426573001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4821,171 +4821,171 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6490 28.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>88209000</v>
+        <v>85466000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>6620000</v>
+        <v>27377000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №281/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №168/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>94829000</v>
+        <v>112843000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>4371000</v>
+        <v>10698000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №99/26 от 27.08.2026</t>
+          <t>Shartnoma №230/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>99200000</v>
+        <v>123541000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>7270000</v>
+        <v>3583000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №12/26 от 28.08.2026</t>
+          <t>Оплата по счет-фактур №9017 за поставленный товар</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>106470000</v>
+        <v>127124000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1085000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>2524000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №260/26</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9486 31.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>105385000</v>
+        <v>129648000</v>
       </c>
     </row>
     <row r="120">
@@ -4997,35 +4997,35 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>3977000</v>
+        <v>2402000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Chirchiq Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>237804138</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000002301637001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №72/26 ОТ 31.08.2026</t>
+          <t>Оплата по с/ф №5665 за поставленный товар</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>109362000</v>
+        <v>132050000</v>
       </c>
     </row>
     <row r="121">
@@ -5035,37 +5035,32 @@
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>3742000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>316462861</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №221/26, НДС 12%</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>113104000</v>
+        <v>131750000</v>
       </c>
     </row>
     <row r="122">
@@ -5075,37 +5070,37 @@
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>2240000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>7041000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №74/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №188/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>115344000</v>
+        <v>124709000</v>
       </c>
     </row>
     <row r="123">
@@ -5115,138 +5110,143 @@
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>2102000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>8258000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9620</t>
+          <t>Оплата за транспортные услуги по договору №246/26</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>117446000</v>
+        <v>116451000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>5477000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Buxoro Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Оплата за продукцию по договору №103/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>117146000</v>
+        <v>121928000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>703000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>2384000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6242</t>
+          <t>Shartnoma №169/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>116443000</v>
+        <v>124312000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>8610000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>1773000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5256,171 +5256,171 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6354</t>
+          <t>Оплата за товар по счет-фактуре №7023 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>107833000</v>
+        <v>126085000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>4107000</v>
+        <v>4578000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №6049 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>111940000</v>
+        <v>130663000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>5801000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>4568000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №35/26</t>
+          <t>Оплата за продукцию по договору №35/26, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>106139000</v>
+        <v>135231000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>2013000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>1113000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>312713817</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000132397891001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №85/26, НДС 12%</t>
+          <t>Оплата за сырье по дог. №31/26 от 04.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>108152000</v>
+        <v>134118000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>33840000</v>
+        <v>1560000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №266/26 от 03.09.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №5411</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>74312000</v>
+        <v>132558000</v>
       </c>
     </row>
     <row r="131">
@@ -5430,37 +5430,37 @@
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>7785000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>322961462</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000483227770001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №129/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №178/26</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>82097000</v>
+        <v>130878000</v>
       </c>
     </row>
     <row r="132">
@@ -5470,77 +5470,72 @@
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>2331000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>5105000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №7/26 от 04.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №7054</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>84428000</v>
+        <v>125773000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>2286000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>12693000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>246439969</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №31/26, НДС 12%</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>86714000</v>
+        <v>113080000</v>
       </c>
     </row>
     <row r="134">
@@ -5552,35 +5547,35 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>1112000</v>
+        <v>6837000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №213/26 от 07.09.2026</t>
+          <t>Оплата по счет-фактуре №948 за поставленный товар</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>87826000</v>
+        <v>119917000</v>
       </c>
     </row>
     <row r="135">
@@ -5592,21 +5587,21 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>1099000</v>
+        <v>3840000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5616,11 +5611,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9369 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan ovar uchun to'lov h/f №3899</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>88925000</v>
+        <v>123757000</v>
       </c>
     </row>
     <row r="136">
@@ -5630,98 +5625,103 @@
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>10013000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>1848000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>346286181</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000345569865001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1278</t>
+          <t>Предоплата за товар по договору №221/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>78912000</v>
+        <v>125605000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>10852000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>12590000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chust Poligraf AJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>255250321</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000850223911001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №151/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4537</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>68060000</v>
+        <v>138195000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>12693000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>2622000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Oqsaroy Bank ATB</t>
+          <t>Saodat Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5731,11 +5731,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по договору №79/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>55367000</v>
+        <v>140817000</v>
       </c>
     </row>
     <row r="139">
@@ -5745,183 +5745,183 @@
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>991000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Ziyo Qurilish MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>365029789</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000252332057001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
+          <t>Аренда помещения за сентябрь, дог. №82/22</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>56358000</v>
+        <v>139377000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>1440000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>3352000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish MChJ</t>
+          <t>Afrosiyob Moy MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>351622961</t>
+          <t>323269310</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000622483227001</t>
+          <t>20208000303426573001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №44/21</t>
+          <t>Оплата за товар по с/ф №493 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>54918000</v>
+        <v>142729000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>7515000</v>
+        <v>2794000</v>
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3840</t>
+          <t>Предоплата за материалы по договору №182/26</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>47403000</v>
+        <v>139935000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46274</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>7793000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>3235000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Buxoro Dori-Darmon MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>342940615</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000849918072001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №2179</t>
+          <t>Оплата за товар по с/ф №3157 от 14.09.2026 в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>39610000</v>
+        <v>143170000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>7828000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>2703000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>340378041</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5931,597 +5931,592 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8916</t>
+          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>31782000</v>
+        <v>145873000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>6639000</v>
+        <v>2582000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5893</t>
+          <t>Shartnoma №183/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>38421000</v>
+        <v>148455000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n"/>
       <c r="D145" s="2" t="n">
-        <v>3009000</v>
+        <v>1893000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5631 за поставленный товар</t>
+          <t>Предоплата за товр по договору №208/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>41430000</v>
+        <v>150348000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>2749000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>1731000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Navro'z Ip-Kalava MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>389741736</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000651397089001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7822 за поставленный товар</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>44179000</v>
+        <v>148617000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>988000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>1731000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №15/26 от 11.09.2026</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>45167000</v>
+        <v>146886000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>7754000</v>
+        <v>65153000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №274/26 от 14.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №7535 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>52921000</v>
+        <v>212039000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46279</v>
+        <v>46285</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1731000</v>
+        <v>26600000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000206639712417</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>51190000</v>
+        <v>185439000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>1731000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>12910000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Shartnoma №274/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>49459000</v>
+        <v>198349000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>8742000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>11054000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Buxoro Dori-Darmon MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>342940615</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000849918072001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №3/26</t>
+          <t>Оплата за товар по счет-фактуре №1420 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>40717000</v>
+        <v>209403000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>1903000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>1408000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Mehnat Dori-Darmon AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>295007701</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000939368176001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №23/26 от 15.09.2026</t>
+          <t>Предоплата за материалы по договору №39/26</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>42620000</v>
+        <v>207995000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>1432000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>2395000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7085 за поставленный товар</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>44052000</v>
+        <v>205600000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>39142000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>6040000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5048 от 16.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №9914</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>83194000</v>
+        <v>199560000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>4156000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>149855000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Namangan Poligraf AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>333131279</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000773430910001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №286/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №196/26</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>87350000</v>
+        <v>49705000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>1943000</v>
+        <v>5010000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1295 за поставленный товар</t>
+          <t>Оплата по с/ф №6452 за поставленный товар</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>89293000</v>
+        <v>54715000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>1788000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Samarqand Moy XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>316462861</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000143455698001</t>
+          <t>20208000540864458001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4043 за поставленный товар</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>91081000</v>
+        <v>53815000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>1026000</v>
+        <v>5435000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6531,37 +6526,37 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8714 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №3635 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>92107000</v>
+        <v>59250000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>13049000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>5167000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>370112444</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000154627596001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6571,77 +6566,77 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №116/26</t>
+          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>79058000</v>
+        <v>64417000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46282</v>
+        <v>46293</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>4356000</v>
+        <v>4782000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7443 от 17.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №7810 за поставленный товар</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>83414000</v>
+        <v>69199000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46282</v>
+        <v>46293</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>1551000</v>
+        <v>3806000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>204101638</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000074776772001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6651,352 +6646,352 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9935 ОТ 17.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №8285 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>84965000</v>
+        <v>73005000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46282</v>
+        <v>46293</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>1137000</v>
+        <v>2481000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7057 за поставленный товар</t>
+          <t>Предоплата за товар по договору №45/26 от 28.09.2026</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>86102000</v>
+        <v>75486000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>1376000</v>
+        <v>2292000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Buxoro Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>271381721</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000239789170001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №17/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №5249 28.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>87478000</v>
+        <v>77778000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46285</v>
+        <v>46293</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>1932000</v>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2395)</t>
+          <t>Lazzat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>374173666</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>16307000206639712417</t>
+          <t>20208000139708929001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2395 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>60878000</v>
+        <v>79710000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>8666000</v>
+        <v>1831000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Navro'z Ip-Kalava MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>389741736</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000651397089001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №247/26 от 21.09.2026</t>
+          <t>Оплата за продукцию по дог. №108/26, НДС 12%</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>69544000</v>
+        <v>81541000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>1797000</v>
-      </c>
+      <c r="C166" s="2" t="n">
+        <v>1548000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Oqtosh Metall XK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>211244471</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000462759637001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2703 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за упаковочные материалы, с/ф №3562</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>71341000</v>
+        <v>79993000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="n">
-        <v>1416000</v>
+        <v>13121000</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Lazzat Poligraf MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>210163830</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000477677234001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Shartnoma №116/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2987 29.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>72757000</v>
+        <v>93114000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
-      <c r="C168" s="2" t="n">
-        <v>33647000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>2357000</v>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Jizzax Polimer MChJ</t>
+          <t>Saodat Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>326232693</t>
+          <t>343996993</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000073034265001</t>
+          <t>20208000104911400001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата за товары огласно счет-фактуре №4233</t>
+          <t>Оплата за продукцию по договору №139/26, НДС 12%</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>39110000</v>
+        <v>95471000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>2156000</v>
+        <v>1929000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Denov Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>246439969</t>
+          <t>245872503</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000311049114001</t>
+          <t>20208000796255585001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №226/26 от 22.09.2026</t>
+          <t>Предоплата за товар по договору №264/26 от 30.09.2026</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>41266000</v>
+        <v>97400000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>7181000</v>
+        <v>300000</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Nihol Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>340378041</t>
+          <t>Oqsaroy Bank ATB</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000870023016001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7006,711 +7001,36 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №108/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>34085000</v>
+        <v>97100000</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>7562000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Samarqand Moy XK</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>316462861</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000143455698001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9228 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>41647000</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>699262000</v>
+      </c>
+      <c r="D171" s="4" t="n">
+        <v>657962000</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>2436000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>39211000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>3290000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Nurafshon Trans Servis AJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>224458725</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000307962555001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6272 24.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>42501000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000702205650001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>41601000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>14757000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>204101638</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000074776772001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №82/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>56358000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>7459000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Navro'z Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>389741736</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000651397089001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Shartnoma №136/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>63817000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>5132000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Tong Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>312713817</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000132397891001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №4/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>68949000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>204101638</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000074776772001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №233/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>70524000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>4692000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Samarqand Moy XK</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>316462861</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000143455698001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №6747 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>75216000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n">
-        <v>2744000</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>246439969</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000311049114001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №8095 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>77960000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n"/>
-      <c r="D181" s="2" t="n">
-        <v>2306000</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Samarqand Moy XK</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>316462861</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000143455698001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Shartnoma №23/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>80266000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>1017000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>204101638</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000074776772001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №8719 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>81283000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>3840000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Nihol Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>340378041</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000870023016001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №222/26</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>77443000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>15810000</v>
-      </c>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Nihol Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>340378041</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000870023016001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №222/26</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>61633000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>30414000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>246439969</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000311049114001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №9837 от 30.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>92047000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>5353000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Bahor Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>246439969</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000311049114001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Оплатаза товар по счет-фактуре №1860 от 30.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>97400000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B187" t="n">
-        <v>279</v>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Oqsaroy Bank ATB</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
         <v>97100000</v>
       </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>682359000</v>
-      </c>
-      <c r="D188" s="4" t="n">
-        <v>641059000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="n">
-        <v>97100000</v>
-      </c>
-      <c r="D189" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
